--- a/financial_models/opportunities/financial_companies/DDM_Monitor_CN.xlsx
+++ b/financial_models/opportunities/financial_companies/DDM_Monitor_CN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\financial_companies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF03B0CF-E4B2-4914-AB62-65413340478B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36C540D-572E-4DBE-827D-647AC21D711D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
